--- a/artfynd/S 3449-2025 artfynd.xlsx
+++ b/artfynd/S 3449-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,48 +884,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126021860</v>
+        <v>137373349</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Herrsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625631</v>
+        <v>625566</v>
       </c>
       <c r="R4" t="n">
-        <v>6985021</v>
+        <v>6985100</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +960,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,55 +984,71 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126021860</t>
+          <t>https://artportalen.se/Sighting/137373349</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126021863</v>
+        <v>137373800</v>
       </c>
       <c r="B5" t="n">
-        <v>80336</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625400</v>
+        <v>625561</v>
       </c>
       <c r="R5" t="n">
-        <v>6985105</v>
+        <v>6985075</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1088,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,18 +1118,1288 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137373800</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137373799</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92162</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>625610</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6985080</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373799</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126021860</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>625631</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6985021</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126021860</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137373796</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79516</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>625626</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6985048</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373796</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137373798</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79516</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>625621</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6985073</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373798</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126021863</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>625400</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6985105</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126021863</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137373348</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58031</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>625606</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6985078</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på granlåga.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373348</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137373350</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58031</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>625506</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6985108</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373350</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137373797</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58190</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>625625</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6985046</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373797</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137373351</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98272</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>625473</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6985118</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373351</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137373801</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98272</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>625538</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6985106</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373801</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137373802</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98272</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-Herrsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>625462</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6985137</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373802</t>
         </is>
       </c>
     </row>
@@ -1092,6 +2409,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3449-2025 artfynd.xlsx
+++ b/artfynd/S 3449-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137373349</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>137373800</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>137373799</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137373351</v>
       </c>
       <c r="B14" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>137373801</v>
       </c>
       <c r="B15" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137373802</v>
       </c>
       <c r="B16" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3449-2025 artfynd.xlsx
+++ b/artfynd/S 3449-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137373349</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>137373800</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>137373799</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137373796</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137373798</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137373348</v>
       </c>
       <c r="B11" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>137373350</v>
       </c>
       <c r="B12" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137373797</v>
       </c>
       <c r="B13" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137373351</v>
       </c>
       <c r="B14" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>137373801</v>
       </c>
       <c r="B15" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137373802</v>
       </c>
       <c r="B16" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3449-2025 artfynd.xlsx
+++ b/artfynd/S 3449-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137373349</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>137373800</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>137373799</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137373796</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137373798</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137373351</v>
       </c>
       <c r="B14" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>137373801</v>
       </c>
       <c r="B15" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137373802</v>
       </c>
       <c r="B16" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3449-2025 artfynd.xlsx
+++ b/artfynd/S 3449-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137373349</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>137373800</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>137373799</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137373796</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137373798</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137373351</v>
       </c>
       <c r="B14" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>137373801</v>
       </c>
       <c r="B15" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137373802</v>
       </c>
       <c r="B16" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3449-2025 artfynd.xlsx
+++ b/artfynd/S 3449-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137373349</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>137373800</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>137373799</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137373796</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137373798</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137373351</v>
       </c>
       <c r="B14" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>137373801</v>
       </c>
       <c r="B15" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137373802</v>
       </c>
       <c r="B16" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3449-2025 artfynd.xlsx
+++ b/artfynd/S 3449-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137373349</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>137373800</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>137373799</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137373796</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137373798</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137373348</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>137373350</v>
       </c>
       <c r="B12" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137373797</v>
       </c>
       <c r="B13" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137373351</v>
       </c>
       <c r="B14" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>137373801</v>
       </c>
       <c r="B15" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137373802</v>
       </c>
       <c r="B16" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
